--- a/法诉案件导入_批次处理明细.xlsx
+++ b/法诉案件导入_批次处理明细.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单处理明细" sheetId="1" r:id="R2e49cc64af684a50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料处理明细" sheetId="2" r:id="R423cbb02622d4e64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务级异常" sheetId="3" r:id="Rce3ddc8f3d694385"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单处理明细" sheetId="1" r:id="R18443a5be9914d58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料处理明细" sheetId="2" r:id="R18df00edaf724af8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务级异常" sheetId="3" r:id="Rc68c1b63c3754e8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误分类说明" sheetId="4" r:id="Ra0d91c3cf5914428"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -24,14 +25,14 @@
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF243447"/>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF202B38"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FF243447"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF202B38"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -44,7 +45,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE9EDF2"/>
+        <x:fgColor rgb="FFF2F4F7"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -52,53 +53,44 @@
     <x:border/>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FFD8E0E8"/>
+        <x:color rgb="FFD9E2EC"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="FFD8E0E8"/>
+        <x:color rgb="FFD9E2EC"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="FFD8E0E8"/>
+        <x:color rgb="FFD9E2EC"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFD8E0E8"/>
+        <x:color rgb="FFD9E2EC"/>
       </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="10">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -302,71 +294,83 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="23" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="34" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="22" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="22" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="20" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="25" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="20" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="21" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="21" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="12" t="str">
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="7" t="str">
         <x:v>导入批次号</x:v>
       </x:c>
-      <x:c r="B1" s="12" t="str">
+      <x:c r="B1" s="7" t="str">
         <x:v>外部资产方</x:v>
       </x:c>
-      <x:c r="C1" s="12" t="str">
+      <x:c r="C1" s="7" t="str">
         <x:v>订单编号</x:v>
       </x:c>
-      <x:c r="D1" s="12" t="str">
+      <x:c r="D1" s="7" t="str">
         <x:v>父订单编号</x:v>
       </x:c>
-      <x:c r="E1" s="12" t="str">
+      <x:c r="E1" s="7" t="str">
         <x:v>客户姓名</x:v>
       </x:c>
-      <x:c r="F1" s="12" t="str">
+      <x:c r="F1" s="7" t="str">
+        <x:v>问题分类</x:v>
+      </x:c>
+      <x:c r="G1" s="7" t="str">
+        <x:v>问题原因</x:v>
+      </x:c>
+      <x:c r="H1" s="7" t="str">
+        <x:v>订单处理状态</x:v>
+      </x:c>
+      <x:c r="I1" s="7" t="str">
+        <x:v>案件状态</x:v>
+      </x:c>
+      <x:c r="J1" s="7" t="str">
+        <x:v>材料状态</x:v>
+      </x:c>
+      <x:c r="K1" s="7" t="str">
+        <x:v>字段校验结果</x:v>
+      </x:c>
+      <x:c r="L1" s="7" t="str">
+        <x:v>材料校验结果</x:v>
+      </x:c>
+      <x:c r="M1" s="7" t="str">
         <x:v>处理来源</x:v>
       </x:c>
-      <x:c r="G1" s="12" t="str">
-        <x:v>字段校验结果</x:v>
-      </x:c>
-      <x:c r="H1" s="12" t="str">
-        <x:v>材料校验结果</x:v>
-      </x:c>
-      <x:c r="I1" s="12" t="str">
-        <x:v>订单处理状态</x:v>
-      </x:c>
-      <x:c r="J1" s="12" t="str">
-        <x:v>案件状态</x:v>
-      </x:c>
-      <x:c r="K1" s="12" t="str">
-        <x:v>材料状态</x:v>
-      </x:c>
-      <x:c r="L1" s="12" t="str">
-        <x:v>失败分类</x:v>
-      </x:c>
-      <x:c r="M1" s="12" t="str">
-        <x:v>失败原因</x:v>
-      </x:c>
-      <x:c r="N1" s="12" t="str">
+      <x:c r="N1" s="7" t="str">
+        <x:v>是否需补传</x:v>
+      </x:c>
+      <x:c r="O1" s="7" t="str">
+        <x:v>建议补传内容</x:v>
+      </x:c>
+      <x:c r="P1" s="7" t="str">
+        <x:v>待补材料</x:v>
+      </x:c>
+      <x:c r="Q1" s="7" t="str">
         <x:v>首次导入时间</x:v>
       </x:c>
-      <x:c r="O1" s="12" t="str">
+      <x:c r="R1" s="7" t="str">
         <x:v>最近处理时间</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="36" customHeight="1">
+    <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
         <x:v>DR202606100001</x:v>
       </x:c>
@@ -376,38 +380,51 @@
       <x:c r="C2" s="9" t="str">
         <x:v>​26012915050167612327</x:v>
       </x:c>
-      <x:c r="D2" s="9" t="str"/>
+      <x:c r="D2" s="9"/>
       <x:c r="E2" s="8" t="str">
         <x:v>张三</x:v>
       </x:c>
       <x:c r="F2" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G2" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H2" s="8" t="str">
+        <x:v>处理成功</x:v>
+      </x:c>
+      <x:c r="I2" s="8" t="str">
+        <x:v>已生效</x:v>
+      </x:c>
+      <x:c r="J2" s="8" t="str">
+        <x:v>材料齐全</x:v>
+      </x:c>
+      <x:c r="K2" s="8" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="L2" s="8" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="M2" s="8" t="str">
         <x:v>首次导入</x:v>
       </x:c>
-      <x:c r="G2" s="8" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="H2" s="8" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="I2" s="8" t="str">
-        <x:v>处理成功</x:v>
-      </x:c>
-      <x:c r="J2" s="8" t="str">
-        <x:v>已生效</x:v>
-      </x:c>
-      <x:c r="K2" s="8" t="str">
-        <x:v>材料齐全</x:v>
-      </x:c>
-      <x:c r="L2" s="8" t="str"/>
-      <x:c r="M2" s="8" t="str"/>
       <x:c r="N2" s="8" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="O2" s="8" t="str">
+        <x:v>无需补传</x:v>
+      </x:c>
+      <x:c r="P2" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="Q2" s="8" t="str">
         <x:v>2026-06-10 20:15:32</x:v>
       </x:c>
-      <x:c r="O2" s="8" t="str">
+      <x:c r="R2" s="8" t="str">
         <x:v>2026-06-10 20:16:08</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="36" customHeight="1">
+    <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="8" t="str">
         <x:v>DR202606100001</x:v>
       </x:c>
@@ -424,35 +441,46 @@
         <x:v>黄丽</x:v>
       </x:c>
       <x:c r="F3" s="8" t="str">
+        <x:v>缺少必填材料</x:v>
+      </x:c>
+      <x:c r="G3" s="8" t="str">
+        <x:v>未匹配到必填材料</x:v>
+      </x:c>
+      <x:c r="H3" s="8" t="str">
+        <x:v>待材料补齐</x:v>
+      </x:c>
+      <x:c r="I3" s="8" t="str">
+        <x:v>待材料激活</x:v>
+      </x:c>
+      <x:c r="J3" s="8" t="str">
+        <x:v>待补必填</x:v>
+      </x:c>
+      <x:c r="K3" s="8" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="L3" s="8" t="str">
+        <x:v>缺少必填材料</x:v>
+      </x:c>
+      <x:c r="M3" s="8" t="str">
         <x:v>首次导入</x:v>
       </x:c>
-      <x:c r="G3" s="8" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="H3" s="8" t="str">
-        <x:v>缺少必填材料</x:v>
-      </x:c>
-      <x:c r="I3" s="8" t="str">
-        <x:v>待材料补齐</x:v>
-      </x:c>
-      <x:c r="J3" s="8" t="str">
-        <x:v>待材料激活</x:v>
-      </x:c>
-      <x:c r="K3" s="8" t="str">
-        <x:v>待补必填</x:v>
-      </x:c>
-      <x:c r="L3" s="8" t="str"/>
-      <x:c r="M3" s="8" t="str">
-        <x:v>缺少必填材料：租赁服务合同</x:v>
-      </x:c>
       <x:c r="N3" s="8" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="O3" s="8" t="str">
+        <x:v>仅上传材料包（必填）</x:v>
+      </x:c>
+      <x:c r="P3" s="8" t="str">
+        <x:v>租赁服务合同</x:v>
+      </x:c>
+      <x:c r="Q3" s="8" t="str">
         <x:v>2026-06-10 20:15:32</x:v>
       </x:c>
-      <x:c r="O3" s="8" t="str">
+      <x:c r="R3" s="8" t="str">
         <x:v>2026-06-10 20:16:08</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="36" customHeight="1">
+    <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="8" t="str">
         <x:v>DR202606100001</x:v>
       </x:c>
@@ -462,40 +490,51 @@
       <x:c r="C4" s="9" t="str">
         <x:v>​26012915050167612331</x:v>
       </x:c>
-      <x:c r="D4" s="9" t="str"/>
+      <x:c r="D4" s="9"/>
       <x:c r="E4" s="8" t="str">
         <x:v>周强</x:v>
       </x:c>
       <x:c r="F4" s="8" t="str">
+        <x:v>缺少非必填材料</x:v>
+      </x:c>
+      <x:c r="G4" s="8" t="str">
+        <x:v>未匹配到非必填材料</x:v>
+      </x:c>
+      <x:c r="H4" s="8" t="str">
+        <x:v>处理成功</x:v>
+      </x:c>
+      <x:c r="I4" s="8" t="str">
+        <x:v>已生效</x:v>
+      </x:c>
+      <x:c r="J4" s="8" t="str">
+        <x:v>待补非必填</x:v>
+      </x:c>
+      <x:c r="K4" s="8" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="L4" s="8" t="str">
+        <x:v>缺少非必填材料</x:v>
+      </x:c>
+      <x:c r="M4" s="8" t="str">
         <x:v>材料补传</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="H4" s="8" t="str">
-        <x:v>缺少非必填材料</x:v>
-      </x:c>
-      <x:c r="I4" s="8" t="str">
-        <x:v>处理成功</x:v>
-      </x:c>
-      <x:c r="J4" s="8" t="str">
-        <x:v>已生效</x:v>
-      </x:c>
-      <x:c r="K4" s="8" t="str">
-        <x:v>待补非必填</x:v>
-      </x:c>
-      <x:c r="L4" s="8" t="str"/>
-      <x:c r="M4" s="8" t="str">
-        <x:v>缺少非必填材料：担保合同</x:v>
-      </x:c>
       <x:c r="N4" s="8" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="O4" s="8" t="str">
+        <x:v>仅上传材料包（非必填）</x:v>
+      </x:c>
+      <x:c r="P4" s="8" t="str">
+        <x:v>担保合同</x:v>
+      </x:c>
+      <x:c r="Q4" s="8" t="str">
         <x:v>2026-06-10 20:15:32</x:v>
       </x:c>
-      <x:c r="O4" s="8" t="str">
+      <x:c r="R4" s="8" t="str">
         <x:v>2026-06-11 10:08:16</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="36" customHeight="1">
+    <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="8" t="str">
         <x:v>DR202606100001</x:v>
       </x:c>
@@ -505,77 +544,155 @@
       <x:c r="C5" s="9" t="str">
         <x:v>​26012915050167612330</x:v>
       </x:c>
-      <x:c r="D5" s="9" t="str"/>
+      <x:c r="D5" s="9"/>
       <x:c r="E5" s="8" t="str">
         <x:v>李明</x:v>
       </x:c>
       <x:c r="F5" s="8" t="str">
+        <x:v>字段格式错误</x:v>
+      </x:c>
+      <x:c r="G5" s="8" t="str">
+        <x:v>身份证号格式错误</x:v>
+      </x:c>
+      <x:c r="H5" s="8" t="str">
+        <x:v>导入失败</x:v>
+      </x:c>
+      <x:c r="I5" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="J5" s="8" t="str">
+        <x:v>未生成</x:v>
+      </x:c>
+      <x:c r="K5" s="8" t="str">
+        <x:v>失败</x:v>
+      </x:c>
+      <x:c r="L5" s="8" t="str">
+        <x:v>未校验</x:v>
+      </x:c>
+      <x:c r="M5" s="8" t="str">
         <x:v>重新导入</x:v>
       </x:c>
-      <x:c r="G5" s="8" t="str">
-        <x:v>失败</x:v>
-      </x:c>
-      <x:c r="H5" s="8" t="str">
-        <x:v>未校验</x:v>
-      </x:c>
-      <x:c r="I5" s="8" t="str">
-        <x:v>导入失败</x:v>
-      </x:c>
-      <x:c r="J5" s="8" t="str"/>
-      <x:c r="K5" s="8" t="str"/>
-      <x:c r="L5" s="8" t="str">
-        <x:v>字段格式错误</x:v>
-      </x:c>
-      <x:c r="M5" s="8" t="str">
-        <x:v>身份证号格式错误</x:v>
-      </x:c>
       <x:c r="N5" s="8" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="O5" s="8" t="str">
+        <x:v>仅上传订单 Excel</x:v>
+      </x:c>
+      <x:c r="P5" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="Q5" s="8" t="str">
         <x:v>2026-06-10 20:15:32</x:v>
       </x:c>
-      <x:c r="O5" s="8" t="str">
+      <x:c r="R5" s="8" t="str">
         <x:v>2026-06-11 10:06:42</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="36" customHeight="1">
+    <x:row r="6" ht="30" customHeight="1">
       <x:c r="A6" s="8" t="str">
-        <x:v>DR202605080001</x:v>
+        <x:v>DR202606100001</x:v>
       </x:c>
       <x:c r="B6" s="8" t="str">
         <x:v>创新</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
+        <x:v>​26012915050167612333</x:v>
+      </x:c>
+      <x:c r="D6" s="9"/>
+      <x:c r="E6" s="8" t="str">
+        <x:v>赵倩</x:v>
+      </x:c>
+      <x:c r="F6" s="8" t="str">
+        <x:v>重复跳过</x:v>
+      </x:c>
+      <x:c r="G6" s="8" t="str">
+        <x:v>原案件已分配或已流转，系统自动跳过，不可覆盖</x:v>
+      </x:c>
+      <x:c r="H6" s="8" t="str">
+        <x:v>重复跳过</x:v>
+      </x:c>
+      <x:c r="I6" s="8" t="str">
+        <x:v>已生效</x:v>
+      </x:c>
+      <x:c r="J6" s="8" t="str">
+        <x:v>未生成</x:v>
+      </x:c>
+      <x:c r="K6" s="8" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="L6" s="8" t="str">
+        <x:v>未校验</x:v>
+      </x:c>
+      <x:c r="M6" s="8" t="str">
+        <x:v>重新导入</x:v>
+      </x:c>
+      <x:c r="N6" s="8" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="O6" s="8" t="str">
+        <x:v>无需补传</x:v>
+      </x:c>
+      <x:c r="P6" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="Q6" s="8" t="str">
+        <x:v>2026-06-10 20:15:32</x:v>
+      </x:c>
+      <x:c r="R6" s="8" t="str">
+        <x:v>2026-06-11 10:08:18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="30" customHeight="1">
+      <x:c r="A7" s="8" t="str">
+        <x:v>DR202605080001</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="str">
+        <x:v>创新</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
         <x:v>​26012915050167612018</x:v>
       </x:c>
-      <x:c r="D6" s="9" t="str"/>
-      <x:c r="E6" s="8" t="str">
+      <x:c r="D7" s="9"/>
+      <x:c r="E7" s="8" t="str">
         <x:v>刘洋</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="str">
+      <x:c r="F7" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="str">
+        <x:v>历史材料包已解析；法诉材料导出请在法诉材料模块操作</x:v>
+      </x:c>
+      <x:c r="H7" s="8" t="str">
+        <x:v>处理成功</x:v>
+      </x:c>
+      <x:c r="I7" s="8" t="str">
+        <x:v>已生效</x:v>
+      </x:c>
+      <x:c r="J7" s="8" t="str">
+        <x:v>材料齐全</x:v>
+      </x:c>
+      <x:c r="K7" s="8" t="str">
+        <x:v>一期已通过</x:v>
+      </x:c>
+      <x:c r="L7" s="8" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="M7" s="8" t="str">
         <x:v>补充历史材料</x:v>
       </x:c>
-      <x:c r="G6" s="8" t="str">
-        <x:v>一期已通过</x:v>
-      </x:c>
-      <x:c r="H6" s="8" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="I6" s="8" t="str">
-        <x:v>处理成功</x:v>
-      </x:c>
-      <x:c r="J6" s="8" t="str">
-        <x:v>已生效</x:v>
-      </x:c>
-      <x:c r="K6" s="8" t="str">
-        <x:v>材料齐全</x:v>
-      </x:c>
-      <x:c r="L6" s="8" t="str"/>
-      <x:c r="M6" s="8" t="str">
-        <x:v>历史材料包已解析；法诉材料导出请在法诉材料模块操作</x:v>
-      </x:c>
-      <x:c r="N6" s="8" t="str">
+      <x:c r="N7" s="8" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="O7" s="8" t="str">
+        <x:v>无需补传</x:v>
+      </x:c>
+      <x:c r="P7" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="Q7" s="8" t="str">
         <x:v>2026-05-08 16:30:21</x:v>
       </x:c>
-      <x:c r="O6" s="8" t="str">
+      <x:c r="R7" s="8" t="str">
         <x:v>2026-07-20 10:02:31</x:v>
       </x:c>
     </x:row>
@@ -588,59 +705,59 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="38" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="36" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="21" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="12" t="str">
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="7" t="str">
         <x:v>导入批次号</x:v>
       </x:c>
-      <x:c r="B1" s="12" t="str">
+      <x:c r="B1" s="7" t="str">
         <x:v>订单编号</x:v>
       </x:c>
-      <x:c r="C1" s="12" t="str">
+      <x:c r="C1" s="7" t="str">
         <x:v>客户姓名</x:v>
       </x:c>
-      <x:c r="D1" s="12" t="str">
+      <x:c r="D1" s="7" t="str">
         <x:v>标准材料类别</x:v>
       </x:c>
-      <x:c r="E1" s="12" t="str">
+      <x:c r="E1" s="7" t="str">
         <x:v>资产方材料名称</x:v>
       </x:c>
-      <x:c r="F1" s="12" t="str">
+      <x:c r="F1" s="7" t="str">
         <x:v>是否必填</x:v>
       </x:c>
-      <x:c r="G1" s="12" t="str">
+      <x:c r="G1" s="7" t="str">
         <x:v>匹配模式</x:v>
       </x:c>
-      <x:c r="H1" s="12" t="str">
+      <x:c r="H1" s="7" t="str">
         <x:v>解析文件</x:v>
       </x:c>
-      <x:c r="I1" s="12" t="str">
+      <x:c r="I1" s="7" t="str">
         <x:v>解析结果</x:v>
       </x:c>
-      <x:c r="J1" s="12" t="str">
+      <x:c r="J1" s="7" t="str">
         <x:v>问题原因</x:v>
       </x:c>
-      <x:c r="K1" s="12" t="str">
+      <x:c r="K1" s="7" t="str">
         <x:v>最近处理时间</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="36" customHeight="1">
+    <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
         <x:v>DR202606100001</x:v>
       </x:c>
-      <x:c r="B2" s="9" t="str">
+      <x:c r="B2" s="8" t="str">
         <x:v>​26012915050167612327</x:v>
       </x:c>
       <x:c r="C2" s="8" t="str">
@@ -664,16 +781,16 @@
       <x:c r="I2" s="8" t="str">
         <x:v>解析通过</x:v>
       </x:c>
-      <x:c r="J2" s="8" t="str"/>
+      <x:c r="J2" s="8"/>
       <x:c r="K2" s="8" t="str">
         <x:v>2026-06-10 20:16:08</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="36" customHeight="1">
+    <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="8" t="str">
         <x:v>DR202606100001</x:v>
       </x:c>
-      <x:c r="B3" s="9" t="str">
+      <x:c r="B3" s="8" t="str">
         <x:v>​26012915050167612328</x:v>
       </x:c>
       <x:c r="C3" s="8" t="str">
@@ -691,7 +808,7 @@
       <x:c r="G3" s="8" t="str">
         <x:v>精确</x:v>
       </x:c>
-      <x:c r="H3" s="8" t="str"/>
+      <x:c r="H3" s="8"/>
       <x:c r="I3" s="8" t="str">
         <x:v>待补必填</x:v>
       </x:c>
@@ -702,11 +819,11 @@
         <x:v>2026-06-10 20:16:08</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="36" customHeight="1">
+    <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="8" t="str">
         <x:v>DR202606100001</x:v>
       </x:c>
-      <x:c r="B4" s="9" t="str">
+      <x:c r="B4" s="8" t="str">
         <x:v>​26012915050167612331</x:v>
       </x:c>
       <x:c r="C4" s="8" t="str">
@@ -724,7 +841,7 @@
       <x:c r="G4" s="8" t="str">
         <x:v>包含</x:v>
       </x:c>
-      <x:c r="H4" s="8" t="str"/>
+      <x:c r="H4" s="8"/>
       <x:c r="I4" s="8" t="str">
         <x:v>待补非必填</x:v>
       </x:c>
@@ -735,38 +852,73 @@
         <x:v>2026-06-11 10:08:16</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="36" customHeight="1">
+    <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="8" t="str">
+        <x:v>DR202606100001</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F5" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G5" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H5" s="8" t="str">
+        <x:v>26012915050167612339_担保合同_01.pdf</x:v>
+      </x:c>
+      <x:c r="I5" s="8" t="str">
+        <x:v>异常文件</x:v>
+      </x:c>
+      <x:c r="J5" s="8" t="str">
+        <x:v>订单不存在或已结清，未纳入案件材料</x:v>
+      </x:c>
+      <x:c r="K5" s="8" t="str">
+        <x:v>2026-06-11 10:08:18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6" s="8" t="str">
         <x:v>DR202605080001</x:v>
       </x:c>
-      <x:c r="B5" s="9" t="str">
+      <x:c r="B6" s="8" t="str">
         <x:v>​26012915050167612018</x:v>
       </x:c>
-      <x:c r="C5" s="8" t="str">
+      <x:c r="C6" s="8" t="str">
         <x:v>刘洋</x:v>
       </x:c>
-      <x:c r="D5" s="8" t="str">
+      <x:c r="D6" s="8" t="str">
         <x:v>身份信息</x:v>
       </x:c>
-      <x:c r="E5" s="8" t="str">
+      <x:c r="E6" s="8" t="str">
         <x:v>人像面</x:v>
       </x:c>
-      <x:c r="F5" s="8" t="str">
+      <x:c r="F6" s="8" t="str">
         <x:v>必填</x:v>
       </x:c>
-      <x:c r="G5" s="8" t="str">
+      <x:c r="G6" s="8" t="str">
         <x:v>包含</x:v>
       </x:c>
-      <x:c r="H5" s="8" t="str">
+      <x:c r="H6" s="8" t="str">
         <x:v>26012915050167612018_人像面_01.jpg</x:v>
       </x:c>
-      <x:c r="I5" s="8" t="str">
+      <x:c r="I6" s="8" t="str">
         <x:v>解析通过</x:v>
       </x:c>
-      <x:c r="J5" s="8" t="str">
+      <x:c r="J6" s="8" t="str">
         <x:v>一期历史批次补充材料</x:v>
       </x:c>
-      <x:c r="K5" s="8" t="str">
+      <x:c r="K6" s="8" t="str">
         <x:v>2026-07-20 10:02:31</x:v>
       </x:c>
     </x:row>
@@ -779,31 +931,31 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="55" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="21" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="12" t="str">
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="7" t="str">
         <x:v>导入批次号</x:v>
       </x:c>
-      <x:c r="B1" s="12" t="str">
+      <x:c r="B1" s="7" t="str">
         <x:v>异常类型</x:v>
       </x:c>
-      <x:c r="C1" s="12" t="str">
+      <x:c r="C1" s="7" t="str">
         <x:v>异常说明</x:v>
       </x:c>
-      <x:c r="D1" s="12" t="str">
+      <x:c r="D1" s="7" t="str">
         <x:v>发生时间</x:v>
       </x:c>
-      <x:c r="E1" s="12" t="str">
+      <x:c r="E1" s="7" t="str">
         <x:v>处理状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="36" customHeight="1">
+    <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
         <x:v>DR202606100001</x:v>
       </x:c>
@@ -820,7 +972,7 @@
         <x:v>待重传</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="36" customHeight="1">
+    <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="8" t="str">
         <x:v>DR202606100001</x:v>
       </x:c>
@@ -835,6 +987,344 @@
       </x:c>
       <x:c r="E3" s="8" t="str">
         <x:v>已恢复</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="54" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="68" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="7" t="str">
+        <x:v>分类/规则</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="str">
+        <x:v>触发场景</x:v>
+      </x:c>
+      <x:c r="C1" s="7" t="str">
+        <x:v>是否阻断</x:v>
+      </x:c>
+      <x:c r="D1" s="7" t="str">
+        <x:v>示例</x:v>
+      </x:c>
+      <x:c r="E1" s="7" t="str">
+        <x:v>提示文案</x:v>
+      </x:c>
+      <x:c r="F1" s="7" t="str">
+        <x:v>处理方式</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="46" customHeight="1">
+      <x:c r="A2" s="8" t="str">
+        <x:v>文件级前置校验</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>订单编号为空、同一Excel订单编号重复、文件超过50MB或订单超过500条</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="str">
+        <x:v>上传阶段拦截，不创建任务</x:v>
+      </x:c>
+      <x:c r="D2" s="8" t="str">
+        <x:v>模板中有重复订单</x:v>
+      </x:c>
+      <x:c r="E2" s="8" t="str">
+        <x:v>订单编号为空：模板中订单编号不能为空，请修正后重新上传。
+重复订单：模板中有重复订单，请修正后重新上传。</x:v>
+      </x:c>
+      <x:c r="F2" s="8" t="str">
+        <x:v>修正Excel后重新上传</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="46" customHeight="1">
+      <x:c r="A3" s="8" t="str">
+        <x:v>模板格式错误</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>文件无法解析、列头名称与模板不一致、缺少必填列等模板问题</x:v>
+      </x:c>
+      <x:c r="C3" s="8" t="str">
+        <x:v>上传阶段拦截，不创建任务</x:v>
+      </x:c>
+      <x:c r="D3" s="8" t="str">
+        <x:v>缺少必填列</x:v>
+      </x:c>
+      <x:c r="E3" s="8" t="str">
+        <x:v>模板缺少必填列【列名】，请修正后重新上传。</x:v>
+      </x:c>
+      <x:c r="F3" s="8" t="str">
+        <x:v>下载最新模板，修正后重新上传</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="46" customHeight="1">
+      <x:c r="A4" s="8" t="str">
+        <x:v>基础必填缺失</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="str">
+        <x:v>导入规则配置为必填或条件必填的字段为空</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="str">
+        <x:v>订单不生成案件</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="str">
+        <x:v>债权金额为空</x:v>
+      </x:c>
+      <x:c r="E4" s="8" t="str">
+        <x:v>【字段名】不能为空</x:v>
+      </x:c>
+      <x:c r="F4" s="8" t="str">
+        <x:v>修正订单Excel后批量补传</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="46" customHeight="1">
+      <x:c r="A5" s="8" t="str">
+        <x:v>字段格式错误</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>身份证号、手机号、日期、枚举值等不符合字段校验规则</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="str">
+        <x:v>订单不生成案件</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>身份证号格式错误</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="str">
+        <x:v>【字段名】字段格式错误</x:v>
+      </x:c>
+      <x:c r="F5" s="8" t="str">
+        <x:v>修正订单Excel后批量补传</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="46" customHeight="1">
+      <x:c r="A6" s="8" t="str">
+        <x:v>金额异常</x:v>
+      </x:c>
+      <x:c r="B6" s="8" t="str">
+        <x:v>金额非数字、为负数或金额关系不合法</x:v>
+      </x:c>
+      <x:c r="C6" s="8" t="str">
+        <x:v>订单不生成案件</x:v>
+      </x:c>
+      <x:c r="D6" s="8" t="str">
+        <x:v>债权金额为负数</x:v>
+      </x:c>
+      <x:c r="E6" s="8" t="str">
+        <x:v>【字段名】金额异常</x:v>
+      </x:c>
+      <x:c r="F6" s="8" t="str">
+        <x:v>修正订单Excel后批量补传</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="46" customHeight="1">
+      <x:c r="A7" s="8" t="str">
+        <x:v>主续关系异常</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="str">
+        <x:v>主订单未同批导入、未结清、父子订单证件号不一致，或主订单已形成案件后再导入续租订单</x:v>
+      </x:c>
+      <x:c r="C7" s="8" t="str">
+        <x:v>订单不生成案件</x:v>
+      </x:c>
+      <x:c r="D7" s="8" t="str">
+        <x:v>主订单已形成案件</x:v>
+      </x:c>
+      <x:c r="E7" s="8" t="str">
+        <x:v>续租订单关联的主订单【父订单编号】已在法诉系统形成案件，不符合续租订单导入条件。</x:v>
+      </x:c>
+      <x:c r="F7" s="8" t="str">
+        <x:v>调整订单组合或主续关系后批量补传订单Excel</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="46" customHeight="1">
+      <x:c r="A8" s="8" t="str">
+        <x:v>跨批次重复</x:v>
+      </x:c>
+      <x:c r="B8" s="8" t="str">
+        <x:v>同一外部资产方+订单编号已在其他批次导入</x:v>
+      </x:c>
+      <x:c r="C8" s="8" t="str">
+        <x:v>上传阶段阻断，不创建本批次记录</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="str">
+        <x:v>订单已在其他批次导入</x:v>
+      </x:c>
+      <x:c r="E8" s="8" t="str">
+        <x:v>该订单已在批次【批次号】导入，本次不允许重复导入。</x:v>
+      </x:c>
+      <x:c r="F8" s="8" t="str">
+        <x:v>更换正确订单后重新上传</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="46" customHeight="1">
+      <x:c r="A9" s="8" t="str">
+        <x:v>重复跳过</x:v>
+      </x:c>
+      <x:c r="B9" s="8" t="str">
+        <x:v>同批次已有案件已分配或已流转，不能自动覆盖</x:v>
+      </x:c>
+      <x:c r="C9" s="8" t="str">
+        <x:v>不覆盖原案件，直接终态</x:v>
+      </x:c>
+      <x:c r="D9" s="8" t="str">
+        <x:v>案件已流转</x:v>
+      </x:c>
+      <x:c r="E9" s="8" t="str">
+        <x:v>原案件已分配或已流转，系统自动跳过，不可覆盖。</x:v>
+      </x:c>
+      <x:c r="F9" s="8" t="str">
+        <x:v>无需重复上传该订单</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="46" customHeight="1">
+      <x:c r="A10" s="8" t="str">
+        <x:v>缺少必填材料</x:v>
+      </x:c>
+      <x:c r="B10" s="8" t="str">
+        <x:v>订单字段校验通过，但未匹配到规则要求的必填材料</x:v>
+      </x:c>
+      <x:c r="C10" s="8" t="str">
+        <x:v>案件待材料激活</x:v>
+      </x:c>
+      <x:c r="D10" s="8" t="str">
+        <x:v>缺少租赁服务合同</x:v>
+      </x:c>
+      <x:c r="E10" s="8" t="str">
+        <x:v>缺少必填材料：{材料名称}</x:v>
+      </x:c>
+      <x:c r="F10" s="8" t="str">
+        <x:v>仅上传材料包；补齐后案件自动生效</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="46" customHeight="1">
+      <x:c r="A11" s="8" t="str">
+        <x:v>缺少非必填材料</x:v>
+      </x:c>
+      <x:c r="B11" s="8" t="str">
+        <x:v>订单已生效，但未匹配到规则要求的非必填材料</x:v>
+      </x:c>
+      <x:c r="C11" s="8" t="str">
+        <x:v>不阻断案件生效</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="str">
+        <x:v>缺少担保合同</x:v>
+      </x:c>
+      <x:c r="E11" s="8" t="str">
+        <x:v>缺少非必填材料：{材料名称}</x:v>
+      </x:c>
+      <x:c r="F11" s="8" t="str">
+        <x:v>按需仅上传材料包</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="46" customHeight="1">
+      <x:c r="A12" s="8" t="str">
+        <x:v>材料包解压异常</x:v>
+      </x:c>
+      <x:c r="B12" s="8" t="str">
+        <x:v>材料包损坏、无法解压或存在不支持的压缩结构</x:v>
+      </x:c>
+      <x:c r="C12" s="8" t="str">
+        <x:v>任务级异常，其他文件可继续解析</x:v>
+      </x:c>
+      <x:c r="D12" s="8" t="str">
+        <x:v>压缩包损坏</x:v>
+      </x:c>
+      <x:c r="E12" s="8" t="str">
+        <x:v>材料包无法解压，请确认压缩包完整后重新上传。</x:v>
+      </x:c>
+      <x:c r="F12" s="8" t="str">
+        <x:v>重新打包材料包后批量补传</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="46" customHeight="1">
+      <x:c r="A13" s="8" t="str">
+        <x:v>异常文件</x:v>
+      </x:c>
+      <x:c r="B13" s="8" t="str">
+        <x:v>文件未匹配到订单、订单已结清或文件不符合材料规则</x:v>
+      </x:c>
+      <x:c r="C13" s="8" t="str">
+        <x:v>不影响其他订单处理</x:v>
+      </x:c>
+      <x:c r="D13" s="8" t="str">
+        <x:v>订单不存在</x:v>
+      </x:c>
+      <x:c r="E13" s="8" t="str">
+        <x:v>订单不存在或已结清，未纳入案件材料。</x:v>
+      </x:c>
+      <x:c r="F13" s="8" t="str">
+        <x:v>核对文件命名和订单状态后重新上传材料包</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="46" customHeight="1">
+      <x:c r="A14" s="8" t="str">
+        <x:v>规则快照异常</x:v>
+      </x:c>
+      <x:c r="B14" s="8" t="str">
+        <x:v>规则快照读取或应用失败</x:v>
+      </x:c>
+      <x:c r="C14" s="8" t="str">
+        <x:v>任务级异常</x:v>
+      </x:c>
+      <x:c r="D14" s="8" t="str">
+        <x:v>规则快照读取超时</x:v>
+      </x:c>
+      <x:c r="E14" s="8" t="str">
+        <x:v>规则快照读取异常，系统将自动重试。</x:v>
+      </x:c>
+      <x:c r="F14" s="8" t="str">
+        <x:v>已恢复无需操作；未恢复时按任务异常说明重传</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="46" customHeight="1">
+      <x:c r="A15" s="8" t="str">
+        <x:v>系统异常</x:v>
+      </x:c>
+      <x:c r="B15" s="8" t="str">
+        <x:v>任务创建后，解析、校验或落库发生技术异常</x:v>
+      </x:c>
+      <x:c r="C15" s="8" t="str">
+        <x:v>任务或订单处理失败</x:v>
+      </x:c>
+      <x:c r="D15" s="8" t="str">
+        <x:v>解析服务异常</x:v>
+      </x:c>
+      <x:c r="E15" s="8" t="str">
+        <x:v>系统异常，请稍后重试。</x:v>
+      </x:c>
+      <x:c r="F15" s="8" t="str">
+        <x:v>在任务级异常查看说明后重传；持续失败联系技术处理</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="46" customHeight="1">
+      <x:c r="A16" s="8" t="str">
+        <x:v>首错输出规则</x:v>
+      </x:c>
+      <x:c r="B16" s="8" t="str">
+        <x:v>同一订单命中多个校验问题时</x:v>
+      </x:c>
+      <x:c r="C16" s="8" t="str">
+        <x:v>不适用</x:v>
+      </x:c>
+      <x:c r="D16" s="8" t="str">
+        <x:v>必填缺失且身份证号格式错误</x:v>
+      </x:c>
+      <x:c r="E16" s="8" t="str">
+        <x:v>仅展示按校验优先级命中的首个订单级失败原因。</x:v>
+      </x:c>
+      <x:c r="F16" s="8" t="str">
+        <x:v>按问题分类和问题原因修正后批量补传</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/法诉案件导入_批次处理明细.xlsx
+++ b/法诉案件导入_批次处理明细.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单处理明细" sheetId="1" r:id="R2de6fa262fda4364"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料处理明细" sheetId="2" r:id="Rdcf677832efa4c74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务级异常" sheetId="3" r:id="R8bd742693d834878"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误分类说明" sheetId="4" r:id="Rffe7e204df13431c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单处理明细" sheetId="1" r:id="R3189ae81efe744c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料处理明细" sheetId="2" r:id="Ra75217ae8f854350"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务级异常" sheetId="3" r:id="R95b5bf083c6c43fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误分类说明" sheetId="4" r:id="R25174d95e34b458c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -962,10 +962,10 @@
     </x:row>
     <x:row r="2" ht="46" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>文件级前置校验</x:v>
+        <x:v>上传前置校验</x:v>
       </x:c>
       <x:c r="B2" s="8" t="str">
-        <x:v>订单编号为空、同一Excel订单编号重复、文件超过50MB或订单超过500条</x:v>
+        <x:v>列头名称与模板不一致，或本Excel内订单编号重复；列顺序可调整，额外列忽略</x:v>
       </x:c>
       <x:c r="C2" s="8" t="str">
         <x:v>上传阶段拦截，不创建任务</x:v>
@@ -974,68 +974,69 @@
         <x:v>模板中有重复订单</x:v>
       </x:c>
       <x:c r="E2" s="8" t="str">
-        <x:v>订单编号为空：模板中订单编号不能为空，请修正后重新上传。
+        <x:v>列头不一致：模板列头【实际列名】与标准模板不一致，请下载最新模板修正后重新上传。
 重复订单：模板中有重复订单，请修正后重新上传。</x:v>
       </x:c>
       <x:c r="F2" s="8" t="str">
-        <x:v>修正Excel后重新上传</x:v>
+        <x:v>下载最新模板或修正重复订单后重新上传</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="46" customHeight="1">
       <x:c r="A3" s="8" t="str">
-        <x:v>模板格式错误</x:v>
+        <x:v>导入前校验</x:v>
       </x:c>
       <x:c r="B3" s="8" t="str">
-        <x:v>文件无法解析、列头名称与模板不一致、缺少必填列等模板问题</x:v>
+        <x:v>必填列缺失、订单编号为空、文件超过50MB或订单超过500条</x:v>
       </x:c>
       <x:c r="C3" s="8" t="str">
-        <x:v>上传阶段拦截，不创建任务</x:v>
+        <x:v>点击导入时拦截，不提交任务</x:v>
       </x:c>
       <x:c r="D3" s="8" t="str">
-        <x:v>缺少必填列</x:v>
+        <x:v>订单编号为空</x:v>
       </x:c>
       <x:c r="E3" s="8" t="str">
-        <x:v>模板缺少必填列【列名】，请修正后重新上传。</x:v>
+        <x:v>订单编号为空：模板中订单编号不能为空，请修正后重新上传。
+缺少必填列：模板缺少必填列【列名】，请修正后重新上传。</x:v>
       </x:c>
       <x:c r="F3" s="8" t="str">
-        <x:v>下载最新模板，修正后重新上传</x:v>
+        <x:v>修正Excel后重新上传</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="46" customHeight="1">
       <x:c r="A4" s="8" t="str">
-        <x:v>基础必填缺失</x:v>
+        <x:v>模板格式错误</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
-        <x:v>导入规则配置为必填或条件必填的字段为空</x:v>
+        <x:v>文件无法解析、列头名称与模板不一致等模板问题</x:v>
       </x:c>
       <x:c r="C4" s="8" t="str">
-        <x:v>订单不生成案件</x:v>
+        <x:v>上传阶段拦截，不创建任务</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
-        <x:v>债权金额为空</x:v>
+        <x:v>文件无法解析</x:v>
       </x:c>
       <x:c r="E4" s="8" t="str">
-        <x:v>【字段名】不能为空</x:v>
+        <x:v>文件无法解析，请确认文件未损坏且格式为xlsx/xls后重新上传。</x:v>
       </x:c>
       <x:c r="F4" s="8" t="str">
-        <x:v>修正订单Excel后批量补传</x:v>
+        <x:v>下载最新模板，修正后重新上传</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="46" customHeight="1">
       <x:c r="A5" s="8" t="str">
-        <x:v>字段格式错误</x:v>
+        <x:v>基础必填缺失</x:v>
       </x:c>
       <x:c r="B5" s="8" t="str">
-        <x:v>身份证号、手机号、日期、枚举值等不符合字段校验规则</x:v>
+        <x:v>导入规则配置为必填或条件必填的字段为空</x:v>
       </x:c>
       <x:c r="C5" s="8" t="str">
         <x:v>订单不生成案件</x:v>
       </x:c>
       <x:c r="D5" s="8" t="str">
-        <x:v>身份证号格式错误</x:v>
+        <x:v>债权金额为空</x:v>
       </x:c>
       <x:c r="E5" s="8" t="str">
-        <x:v>【字段名】字段格式错误</x:v>
+        <x:v>【字段名】不能为空</x:v>
       </x:c>
       <x:c r="F5" s="8" t="str">
         <x:v>修正订单Excel后批量补传</x:v>
@@ -1043,19 +1044,19 @@
     </x:row>
     <x:row r="6" ht="46" customHeight="1">
       <x:c r="A6" s="8" t="str">
-        <x:v>金额异常</x:v>
+        <x:v>字段格式错误</x:v>
       </x:c>
       <x:c r="B6" s="8" t="str">
-        <x:v>金额非数字、为负数或金额关系不合法</x:v>
+        <x:v>身份证号、手机号、日期、枚举值等不符合字段校验规则</x:v>
       </x:c>
       <x:c r="C6" s="8" t="str">
         <x:v>订单不生成案件</x:v>
       </x:c>
       <x:c r="D6" s="8" t="str">
-        <x:v>债权金额为负数</x:v>
+        <x:v>身份证号格式错误</x:v>
       </x:c>
       <x:c r="E6" s="8" t="str">
-        <x:v>【字段名】金额异常</x:v>
+        <x:v>【字段名】字段格式错误</x:v>
       </x:c>
       <x:c r="F6" s="8" t="str">
         <x:v>修正订单Excel后批量补传</x:v>
@@ -1063,201 +1064,221 @@
     </x:row>
     <x:row r="7" ht="46" customHeight="1">
       <x:c r="A7" s="8" t="str">
-        <x:v>主续关系异常</x:v>
+        <x:v>金额异常</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
-        <x:v>主订单未同批导入、未结清、父子订单证件号不一致，或主订单已形成案件后再导入续租订单</x:v>
+        <x:v>金额非数字、为负数或金额关系不合法</x:v>
       </x:c>
       <x:c r="C7" s="8" t="str">
         <x:v>订单不生成案件</x:v>
       </x:c>
       <x:c r="D7" s="8" t="str">
-        <x:v>主订单已形成案件</x:v>
+        <x:v>债权金额为负数</x:v>
       </x:c>
       <x:c r="E7" s="8" t="str">
-        <x:v>续租订单关联的主订单【父订单编号】已在法诉系统形成案件，不符合续租订单导入条件。</x:v>
+        <x:v>【字段名】金额异常</x:v>
       </x:c>
       <x:c r="F7" s="8" t="str">
-        <x:v>调整订单组合或主续关系后批量补传订单Excel</x:v>
+        <x:v>修正订单Excel后批量补传</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="46" customHeight="1">
       <x:c r="A8" s="8" t="str">
-        <x:v>跨批次重复</x:v>
+        <x:v>主子订单校验异常</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
-        <x:v>同一外部资产方+订单编号已在其他批次导入</x:v>
+        <x:v>主订单未同批导入、未结清、父子订单证件号不一致；系统仅已有主订单案件时，本次主子订单导入或仅续租订单导入均不允许更新</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
-        <x:v>上传阶段阻断，不创建本批次记录</x:v>
+        <x:v>订单不生成案件</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
-        <x:v>订单已在其他批次导入</x:v>
+        <x:v>主订单已形成案件</x:v>
       </x:c>
       <x:c r="E8" s="8" t="str">
-        <x:v>该订单已在批次【批次号】导入，本次不允许重复导入。</x:v>
+        <x:v>续租订单关联的主订单【父订单编号】已在法诉系统形成案件，不符合续租订单导入条件。</x:v>
       </x:c>
       <x:c r="F8" s="8" t="str">
-        <x:v>更换正确订单后重新上传</x:v>
+        <x:v>调整订单组合或主子订单关系后批量补传订单Excel</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="46" customHeight="1">
       <x:c r="A9" s="8" t="str">
-        <x:v>重复跳过</x:v>
+        <x:v>跨批次重复</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
-        <x:v>同批次已有案件已分配或已流转，不能自动覆盖</x:v>
+        <x:v>同一外部资产方+订单编号已在其他批次导入</x:v>
       </x:c>
       <x:c r="C9" s="8" t="str">
-        <x:v>不覆盖原案件，直接终态</x:v>
+        <x:v>上传阶段阻断，不创建本批次记录</x:v>
       </x:c>
       <x:c r="D9" s="8" t="str">
-        <x:v>案件已流转</x:v>
+        <x:v>订单已在其他批次导入</x:v>
       </x:c>
       <x:c r="E9" s="8" t="str">
-        <x:v>原案件已分配或已流转，系统自动跳过，不可覆盖。</x:v>
+        <x:v>该订单已在批次【批次号】导入，本次不允许重复导入。</x:v>
       </x:c>
       <x:c r="F9" s="8" t="str">
-        <x:v>无需重复上传该订单</x:v>
+        <x:v>更换正确订单后重新上传</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="46" customHeight="1">
       <x:c r="A10" s="8" t="str">
-        <x:v>缺少必填材料</x:v>
+        <x:v>重复跳过</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
-        <x:v>订单字段校验通过，但未匹配到规则要求的必填材料</x:v>
+        <x:v>同批次已有案件已分配或已流转，不能自动覆盖</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
-        <x:v>案件待材料激活</x:v>
+        <x:v>不覆盖原案件，直接终态</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
-        <x:v>缺少租赁服务合同</x:v>
+        <x:v>案件已流转</x:v>
       </x:c>
       <x:c r="E10" s="8" t="str">
-        <x:v>缺少必填材料：{材料名称}</x:v>
+        <x:v>原案件已分配或已流转，系统自动跳过，不可覆盖。</x:v>
       </x:c>
       <x:c r="F10" s="8" t="str">
-        <x:v>仅上传材料包；补齐后案件自动生效</x:v>
+        <x:v>无需重复上传该订单</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="46" customHeight="1">
       <x:c r="A11" s="8" t="str">
-        <x:v>缺少非必填材料</x:v>
+        <x:v>缺少必填材料</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
-        <x:v>订单已生效，但未匹配到规则要求的非必填材料</x:v>
+        <x:v>订单字段校验通过，但未匹配到规则要求的必填材料</x:v>
       </x:c>
       <x:c r="C11" s="8" t="str">
-        <x:v>不阻断案件生效</x:v>
+        <x:v>案件待材料激活</x:v>
       </x:c>
       <x:c r="D11" s="8" t="str">
-        <x:v>缺少担保合同</x:v>
+        <x:v>缺少租赁服务合同</x:v>
       </x:c>
       <x:c r="E11" s="8" t="str">
-        <x:v>缺少非必填材料：{材料名称}</x:v>
+        <x:v>缺少必填材料：{材料名称}</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
-        <x:v>按需仅上传材料包</x:v>
+        <x:v>仅上传材料包；补齐后案件自动生效</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="46" customHeight="1">
       <x:c r="A12" s="8" t="str">
-        <x:v>材料包解压异常</x:v>
+        <x:v>缺少非必填材料</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
-        <x:v>材料包损坏、无法解压或存在不支持的压缩结构</x:v>
+        <x:v>订单已生效，但未匹配到规则要求的非必填材料</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
-        <x:v>任务级异常，其他文件可继续解析</x:v>
+        <x:v>不阻断案件生效</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str">
-        <x:v>压缩包损坏</x:v>
+        <x:v>缺少担保合同</x:v>
       </x:c>
       <x:c r="E12" s="8" t="str">
-        <x:v>材料包无法解压，请确认压缩包完整后重新上传。</x:v>
+        <x:v>缺少非必填材料：{材料名称}</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str">
-        <x:v>重新打包材料包后批量补传</x:v>
+        <x:v>按需仅上传材料包</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="46" customHeight="1">
       <x:c r="A13" s="8" t="str">
-        <x:v>异常文件</x:v>
+        <x:v>材料包解压异常</x:v>
       </x:c>
       <x:c r="B13" s="8" t="str">
-        <x:v>文件未匹配到订单、订单已结清或文件不符合材料规则</x:v>
+        <x:v>材料包损坏、无法解压或存在不支持的压缩结构</x:v>
       </x:c>
       <x:c r="C13" s="8" t="str">
-        <x:v>不影响其他订单处理</x:v>
+        <x:v>任务级异常，其他文件可继续解析</x:v>
       </x:c>
       <x:c r="D13" s="8" t="str">
-        <x:v>订单不存在</x:v>
+        <x:v>压缩包损坏</x:v>
       </x:c>
       <x:c r="E13" s="8" t="str">
-        <x:v>订单不存在或已结清，未纳入案件材料。</x:v>
+        <x:v>材料包无法解压，请确认压缩包完整后重新上传。</x:v>
       </x:c>
       <x:c r="F13" s="8" t="str">
-        <x:v>核对文件命名和订单状态后重新上传材料包</x:v>
+        <x:v>重新打包材料包后批量补传</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="46" customHeight="1">
       <x:c r="A14" s="8" t="str">
-        <x:v>规则快照异常</x:v>
+        <x:v>异常文件</x:v>
       </x:c>
       <x:c r="B14" s="8" t="str">
-        <x:v>规则快照读取或应用失败</x:v>
+        <x:v>文件未匹配到订单、订单已结清或文件不符合材料规则</x:v>
       </x:c>
       <x:c r="C14" s="8" t="str">
-        <x:v>任务级异常</x:v>
+        <x:v>不影响其他订单处理</x:v>
       </x:c>
       <x:c r="D14" s="8" t="str">
-        <x:v>规则快照读取超时</x:v>
+        <x:v>订单不存在</x:v>
       </x:c>
       <x:c r="E14" s="8" t="str">
-        <x:v>规则快照读取异常，系统将自动重试。</x:v>
+        <x:v>订单不存在或已结清，未纳入案件材料。</x:v>
       </x:c>
       <x:c r="F14" s="8" t="str">
-        <x:v>已恢复无需操作；未恢复时按任务异常说明重传</x:v>
+        <x:v>核对文件命名和订单状态后重新上传材料包</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="46" customHeight="1">
       <x:c r="A15" s="8" t="str">
-        <x:v>系统异常</x:v>
+        <x:v>规则快照异常</x:v>
       </x:c>
       <x:c r="B15" s="8" t="str">
-        <x:v>任务创建后，解析、校验或落库发生技术异常</x:v>
+        <x:v>规则快照读取或应用失败</x:v>
       </x:c>
       <x:c r="C15" s="8" t="str">
-        <x:v>任务或订单处理失败</x:v>
+        <x:v>任务级异常</x:v>
       </x:c>
       <x:c r="D15" s="8" t="str">
-        <x:v>解析服务异常</x:v>
+        <x:v>规则快照读取超时</x:v>
       </x:c>
       <x:c r="E15" s="8" t="str">
-        <x:v>系统异常，请稍后重试。</x:v>
+        <x:v>规则快照读取异常，系统将自动重试。</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
-        <x:v>在任务级异常查看说明后重传；持续失败联系技术处理</x:v>
+        <x:v>已恢复无需操作；未恢复时按任务异常说明重传</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="46" customHeight="1">
       <x:c r="A16" s="8" t="str">
+        <x:v>系统异常</x:v>
+      </x:c>
+      <x:c r="B16" s="8" t="str">
+        <x:v>任务创建后，解析、校验或落库发生技术异常</x:v>
+      </x:c>
+      <x:c r="C16" s="8" t="str">
+        <x:v>任务或订单处理失败</x:v>
+      </x:c>
+      <x:c r="D16" s="8" t="str">
+        <x:v>解析服务异常</x:v>
+      </x:c>
+      <x:c r="E16" s="8" t="str">
+        <x:v>系统异常，请稍后重试。</x:v>
+      </x:c>
+      <x:c r="F16" s="8" t="str">
+        <x:v>在任务级异常查看说明后重传；持续失败联系技术处理</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="30" customHeight="1">
+      <x:c r="A17" s="8" t="str">
         <x:v>首错输出规则</x:v>
       </x:c>
-      <x:c r="B16" s="8" t="str">
+      <x:c r="B17" s="8" t="str">
         <x:v>同一订单命中多个校验问题时</x:v>
       </x:c>
-      <x:c r="C16" s="8" t="str">
+      <x:c r="C17" s="8" t="str">
         <x:v>不适用</x:v>
       </x:c>
-      <x:c r="D16" s="8" t="str">
+      <x:c r="D17" s="8" t="str">
         <x:v>必填缺失且身份证号格式错误</x:v>
       </x:c>
-      <x:c r="E16" s="8" t="str">
+      <x:c r="E17" s="8" t="str">
         <x:v>仅展示按校验优先级命中的首个订单级失败原因。</x:v>
       </x:c>
-      <x:c r="F16" s="8" t="str">
+      <x:c r="F17" s="8" t="str">
         <x:v>按问题分类和问题原因修正后批量补传</x:v>
       </x:c>
     </x:row>

--- a/法诉案件导入_批次处理明细.xlsx
+++ b/法诉案件导入_批次处理明细.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单处理明细" sheetId="1" r:id="R3189ae81efe744c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料处理明细" sheetId="2" r:id="Ra75217ae8f854350"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务级异常" sheetId="3" r:id="R95b5bf083c6c43fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误分类说明" sheetId="4" r:id="R25174d95e34b458c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单处理明细" sheetId="1" r:id="Rf91f7eab081f4694"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料处理明细" sheetId="2" r:id="R6694182979eb45ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务级异常" sheetId="3" r:id="Rd899bc4824324939"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误分类说明" sheetId="4" r:id="R2e488cc4656c49ff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -502,21 +502,19 @@
       <x:c r="B5" s="8" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="C5" s="9" t="str">
-        <x:v>​26012915050167612330</x:v>
-      </x:c>
+      <x:c r="C5" s="9" t="str"/>
       <x:c r="D5" s="9"/>
       <x:c r="E5" s="8" t="str">
-        <x:v>李明</x:v>
+        <x:v>吴空</x:v>
       </x:c>
       <x:c r="F5" s="8" t="str">
         <x:v>导入失败</x:v>
       </x:c>
       <x:c r="G5" s="8" t="str">
-        <x:v>字段格式错误</x:v>
+        <x:v>导入前校验</x:v>
       </x:c>
       <x:c r="H5" s="8" t="str">
-        <x:v>身份证号格式错误</x:v>
+        <x:v>模板中订单编号不能为空，请修正后重新上传。</x:v>
       </x:c>
       <x:c r="I5" s="8" t="str">
         <x:v>-</x:v>
@@ -537,7 +535,7 @@
         <x:v>2026-06-10 20:15:32</x:v>
       </x:c>
       <x:c r="O5" s="8" t="str">
-        <x:v>2026-06-11 10:06:42</x:v>
+        <x:v>2026-06-11 10:05:38</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
@@ -548,32 +546,32 @@
         <x:v>创新</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>​26012915050167612333</x:v>
+        <x:v>​26012915050167612330</x:v>
       </x:c>
       <x:c r="D6" s="9"/>
       <x:c r="E6" s="8" t="str">
-        <x:v>赵倩</x:v>
+        <x:v>李明</x:v>
       </x:c>
       <x:c r="F6" s="8" t="str">
-        <x:v>重复跳过</x:v>
+        <x:v>导入失败</x:v>
       </x:c>
       <x:c r="G6" s="8" t="str">
-        <x:v>重复跳过</x:v>
+        <x:v>字段格式错误</x:v>
       </x:c>
       <x:c r="H6" s="8" t="str">
-        <x:v>原案件已分配或已流转，系统自动跳过，不可覆盖。</x:v>
+        <x:v>身份证号格式错误</x:v>
       </x:c>
       <x:c r="I6" s="8" t="str">
-        <x:v>已生效</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="J6" s="8" t="str">
         <x:v>未生成</x:v>
       </x:c>
       <x:c r="K6" s="8" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="L6" s="8" t="str">
-        <x:v>无需补传</x:v>
+        <x:v>仅上传订单 Excel</x:v>
       </x:c>
       <x:c r="M6" s="8" t="str">
         <x:v>-</x:v>
@@ -582,37 +580,37 @@
         <x:v>2026-06-10 20:15:32</x:v>
       </x:c>
       <x:c r="O6" s="8" t="str">
-        <x:v>2026-06-11 10:08:18</x:v>
+        <x:v>2026-06-11 10:06:42</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
       <x:c r="A7" s="8" t="str">
-        <x:v>DR202605080001</x:v>
+        <x:v>DR202606100001</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
         <x:v>创新</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>​26012915050167612018</x:v>
+        <x:v>​26012915050167612333</x:v>
       </x:c>
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="8" t="str">
-        <x:v>刘洋</x:v>
+        <x:v>赵倩</x:v>
       </x:c>
       <x:c r="F7" s="8" t="str">
-        <x:v>处理成功</x:v>
+        <x:v>重复跳过</x:v>
       </x:c>
       <x:c r="G7" s="8" t="str">
-        <x:v>-</x:v>
+        <x:v>重复跳过</x:v>
       </x:c>
       <x:c r="H7" s="8" t="str">
-        <x:v>-</x:v>
+        <x:v>原案件已分配或已流转，系统自动跳过，不可覆盖。</x:v>
       </x:c>
       <x:c r="I7" s="8" t="str">
         <x:v>已生效</x:v>
       </x:c>
       <x:c r="J7" s="8" t="str">
-        <x:v>材料齐全</x:v>
+        <x:v>未生成</x:v>
       </x:c>
       <x:c r="K7" s="8" t="str">
         <x:v>否</x:v>
@@ -624,9 +622,54 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="N7" s="8" t="str">
+        <x:v>2026-06-10 20:15:32</x:v>
+      </x:c>
+      <x:c r="O7" s="8" t="str">
+        <x:v>2026-06-11 10:08:18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="30" customHeight="1">
+      <x:c r="A8" s="8" t="str">
+        <x:v>DR202605080001</x:v>
+      </x:c>
+      <x:c r="B8" s="8" t="str">
+        <x:v>创新</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
+        <x:v>​26012915050167612018</x:v>
+      </x:c>
+      <x:c r="D8" s="9"/>
+      <x:c r="E8" s="8" t="str">
+        <x:v>刘洋</x:v>
+      </x:c>
+      <x:c r="F8" s="8" t="str">
+        <x:v>处理成功</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H8" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I8" s="8" t="str">
+        <x:v>已生效</x:v>
+      </x:c>
+      <x:c r="J8" s="8" t="str">
+        <x:v>材料齐全</x:v>
+      </x:c>
+      <x:c r="K8" s="8" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="L8" s="8" t="str">
+        <x:v>无需补传</x:v>
+      </x:c>
+      <x:c r="M8" s="8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="N8" s="8" t="str">
         <x:v>2026-05-08 16:30:21</x:v>
       </x:c>
-      <x:c r="O7" s="8" t="str">
+      <x:c r="O8" s="8" t="str">
         <x:v>2026-07-20 10:02:31</x:v>
       </x:c>
     </x:row>
@@ -986,10 +1029,10 @@
         <x:v>导入前校验</x:v>
       </x:c>
       <x:c r="B3" s="8" t="str">
-        <x:v>必填列缺失、订单编号为空、文件超过50MB或订单超过500条</x:v>
+        <x:v>必填列缺失、订单编号为空等行级问题</x:v>
       </x:c>
       <x:c r="C3" s="8" t="str">
-        <x:v>点击导入时拦截，不提交任务</x:v>
+        <x:v>写入订单处理明细，不影响其它订单导入</x:v>
       </x:c>
       <x:c r="D3" s="8" t="str">
         <x:v>订单编号为空</x:v>
@@ -999,7 +1042,7 @@
 缺少必填列：模板缺少必填列【列名】，请修正后重新上传。</x:v>
       </x:c>
       <x:c r="F3" s="8" t="str">
-        <x:v>修正Excel后重新上传</x:v>
+        <x:v>修正问题行后通过编辑或批量补传重新上传</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="46" customHeight="1">
